--- a/2026/BELTRAN 34/ENERO/Enero BELTRAN.xlsx
+++ b/2026/BELTRAN 34/ENERO/Enero BELTRAN.xlsx
@@ -5,27 +5,27 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BELTRAN 34\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\BELTRAN 34\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A69918-1B91-4DC6-A161-F667FC61A148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41665642-4AD6-41D6-831B-5C7ADCF594A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$98</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$103</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="130">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -231,9 +231,6 @@
     <t>Seguro integral de consorcio - Sancor Seguro</t>
   </si>
   <si>
-    <t>METROGAS</t>
-  </si>
-  <si>
     <t>Abono mantenimiento de cuenta e impuestos</t>
   </si>
   <si>
@@ -324,9 +321,6 @@
     <t>TELEFONO : 11-5320-2676 - MAIL: coronelbeltran34rc@gmail.com - OFICINA CON CITA PREVIA - DR MELO 2958 8° PISO</t>
   </si>
   <si>
-    <t>Transf 30/12</t>
-  </si>
-  <si>
     <t>EDESUR - Nro. De cliente 04238360</t>
   </si>
   <si>
@@ -361,24 +355,6 @@
   </si>
   <si>
     <t>Gastos bancarios</t>
-  </si>
-  <si>
-    <t>Estimados propietarios e inquilinos,
-Queremos informarles que, en las últimas expensas enviadas por la administración saliente (Sra. Mara), se detectó un error en la fórmula que calculaba el saldo total a abonar.
-Dicho error hacía que, en la columna “Saldo a abonar”, solo se contemplaran las expensas ordinarias, sin sumarse las expensas extraordinarias correspondientes a cada unidad funcional.
-Entendemos y aclaramos que:
- • Muchas personas abonaron correctamente el importe que figuraba en esa columna, lo cual está perfecto.
- • Otras personas detectaron el error y, por sus propios medios, sumaron las expensas ordinarias y extraordinarias, abonando el total correcto.
-Por este motivo, algunos propietarios o inquilinos que pagaron el importe indicado en la columna “Saldo a abonar” pueden visualizar ahora un saldo pendiente, el cual no se debe a falta de pago, sino a este error administrativo ocurrido durante el traspaso de administración.
-Queremos llevar tranquilidad:
-👉 No se aplicarán intereses ni recargos por esta diferencia.
-👉 La situación será regularizada de forma ordenada y transparente.
-Agradecemos la comprensión de todos y quedamos a disposición ante cualquier consulta.</t>
-  </si>
-  <si>
-    <t>PREVISION ORDINARIA: Se incluye una previsión ordinaria debido a la urgente reparación del ascensor, dañado durante una mudanza realizada el día 30 fuera de horario.
-Si bien el arreglo será imputado a la unidad funcional responsable, la previsión se realiza de forma provisoria para poder efectuar la reparación de inmediato y dejar el ascensor operativo.
-Una vez recuperado el importe correspondiente, el gasto no quedará a cargo del consorcio.</t>
   </si>
   <si>
     <t xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
@@ -387,18 +363,9 @@
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </t>
   </si>
   <si>
-    <t>Traspaso de administracion - Sr. Mara</t>
-  </si>
-  <si>
     <t>VTO 16/02</t>
   </si>
   <si>
-    <t xml:space="preserve">Lomas Lift - Abono mantenimiento de ascensor mes de ENERO </t>
-  </si>
-  <si>
-    <t>Honorarios administracion saliente - se adeudaban de DICIEMBRE</t>
-  </si>
-  <si>
     <t>Mes de DICIEMBRE</t>
   </si>
   <si>
@@ -406,6 +373,51 @@
   </si>
   <si>
     <t>Transf 07/01</t>
+  </si>
+  <si>
+    <t>Transf 05/01</t>
+  </si>
+  <si>
+    <t>Debito 13/01</t>
+  </si>
+  <si>
+    <t>Ascensores Contessi - Provision y colocacion comando de techo en la cabina de ascensor CUOTA 1 DE 3</t>
+  </si>
+  <si>
+    <t>Transf 12/01</t>
+  </si>
+  <si>
+    <t>Ascensores Contessi - Reparacion según informe (ver informe y factura de reparacion de la apertura de bomberos)</t>
+  </si>
+  <si>
+    <t>Transf 30/01</t>
+  </si>
+  <si>
+    <t>Ef.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascensores Contessi - Colocacion de barreras de seguridad - Anticipo </t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA</t>
+  </si>
+  <si>
+    <t>Matias Gonzalez</t>
+  </si>
+  <si>
+    <t>Claudio Martuccio</t>
+  </si>
+  <si>
+    <t>Carla Fabiana Silva</t>
+  </si>
+  <si>
+    <t>Bonificaciones banco santander</t>
+  </si>
+  <si>
+    <t>Dateas - solicitud de datos inicio ejecucion de datos</t>
+  </si>
+  <si>
+    <t>LA ADMINISTRACION CUENTA CON GASTOS A RECUPERAR (GASTOS QUE SE ABONAR EN EFECTIVO) QUE SUCEDERAN HASTA TRASPASAR LOS SEGUROS $67.154. LA SRA SOLEDAD TIENE A FAVOR DEL SERVICIO DE LIMPIEZA DEL MES DE FEBRERO $78.800</t>
   </si>
 </sst>
 </file>
@@ -731,7 +743,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -930,14 +942,8 @@
         <bgColor indexed="9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="40">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1389,21 +1395,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1461,7 +1452,7 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1637,7 +1628,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="43" fillId="2" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1645,7 +1635,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1661,15 +1651,6 @@
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1680,15 +1661,21 @@
     <xf numFmtId="10" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="44" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1701,10 +1688,43 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1716,82 +1736,38 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="43" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -2187,17 +2163,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L98"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L103"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2210,13 +2186,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B2" s="97"/>
       <c r="C2" s="97"/>
       <c r="D2" s="97"/>
     </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1">
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1">
       <c r="A3" s="97" t="s">
         <v>65</v>
       </c>
@@ -2225,74 +2201,74 @@
       <c r="D3" s="97"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A4" s="167" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="167"/>
+      <c r="A4" s="156" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="156"/>
       <c r="C4" s="98"/>
       <c r="D4" s="98"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="167"/>
-      <c r="B5" s="167"/>
+      <c r="A5" s="156"/>
+      <c r="B5" s="156"/>
       <c r="C5" s="98"/>
       <c r="D5" s="98"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="167"/>
-      <c r="B6" s="167"/>
+      <c r="A6" s="156"/>
+      <c r="B6" s="156"/>
       <c r="C6" s="98"/>
       <c r="D6" s="98"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="167"/>
-      <c r="B7" s="167"/>
+      <c r="A7" s="156"/>
+      <c r="B7" s="156"/>
       <c r="C7" s="98"/>
       <c r="D7" s="98"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="166" t="s">
-        <v>116</v>
+      <c r="B9" s="164" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="166"/>
+      <c r="B10" s="164"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="166"/>
+      <c r="B11" s="164"/>
     </row>
     <row r="13" spans="1:4" hidden="1"/>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="168" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" s="168"/>
-      <c r="C14" s="168"/>
-      <c r="D14" s="168"/>
+      <c r="A14" s="159" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="159"/>
+      <c r="C14" s="159"/>
+      <c r="D14" s="159"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="168"/>
-      <c r="B15" s="168"/>
-      <c r="C15" s="168"/>
-      <c r="D15" s="168"/>
+      <c r="A15" s="159"/>
+      <c r="B15" s="159"/>
+      <c r="C15" s="159"/>
+      <c r="D15" s="159"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="168"/>
-      <c r="B16" s="168"/>
-      <c r="C16" s="168"/>
-      <c r="D16" s="168"/>
+      <c r="A16" s="159"/>
+      <c r="B16" s="159"/>
+      <c r="C16" s="159"/>
+      <c r="D16" s="159"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="168"/>
-      <c r="B17" s="168"/>
-      <c r="C17" s="168"/>
-      <c r="D17" s="168"/>
+      <c r="A17" s="159"/>
+      <c r="B17" s="159"/>
+      <c r="C17" s="159"/>
+      <c r="D17" s="159"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1"/>
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1"/>
     <row r="21" spans="1:7">
       <c r="A21" s="9" t="s">
         <v>21</v>
@@ -2303,30 +2279,31 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="23" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B22" s="23"/>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
+      <c r="G22" s="33"/>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="70" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B23" s="70"/>
-      <c r="C23" s="145">
-        <v>131200</v>
+      <c r="C23" s="144">
+        <v>184320</v>
       </c>
       <c r="D23" s="70"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="146" t="s">
+      <c r="A24" s="145" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="146"/>
+      <c r="B24" s="145"/>
       <c r="C24" s="95">
         <f>SUM(C23:C23)</f>
-        <v>131200</v>
+        <v>184320</v>
       </c>
       <c r="D24" s="71"/>
     </row>
@@ -2355,10 +2332,10 @@
       <c r="D28" s="99"/>
     </row>
     <row r="29" spans="1:7" hidden="1">
-      <c r="A29" s="146" t="s">
+      <c r="A29" s="145" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="147"/>
+      <c r="B29" s="146"/>
       <c r="C29" s="41">
         <f>SUM(C25:C28)</f>
         <v>0</v>
@@ -2373,7 +2350,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="72">
         <f>C24+C29</f>
-        <v>131200</v>
+        <v>184320</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
@@ -2389,539 +2366,572 @@
     </row>
     <row r="32" spans="1:7" ht="22.5" customHeight="1">
       <c r="A32" s="128" t="s">
-        <v>106</v>
-      </c>
-      <c r="B32" s="148"/>
+        <v>104</v>
+      </c>
+      <c r="B32" s="147"/>
       <c r="C32" s="111">
         <v>0</v>
       </c>
       <c r="D32" s="109"/>
+      <c r="F32" s="33">
+        <v>73700</v>
+      </c>
       <c r="G32" s="12"/>
     </row>
-    <row r="33" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A33" s="128" t="s">
+    <row r="33" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A33" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="22"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="72">
+        <f>SUM(C32:C32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A34" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="22"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="47"/>
+    </row>
+    <row r="35" spans="1:6" s="30" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A35" s="157" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="158"/>
+      <c r="C35" s="113">
+        <v>23077</v>
+      </c>
+      <c r="D35" s="108" t="s">
+        <v>121</v>
+      </c>
+      <c r="F35" s="193">
+        <f>C35*2</f>
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="22.5" customHeight="1">
+      <c r="A36" s="157" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="158"/>
+      <c r="C36" s="114">
+        <v>152897</v>
+      </c>
+      <c r="D36" s="108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A37" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="74">
+        <f>SUM(C35:C36)</f>
+        <v>175974</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" hidden="1">
+      <c r="A38" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="75"/>
+    </row>
+    <row r="39" spans="1:6" hidden="1">
+      <c r="A39" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="115"/>
+      <c r="D39" s="108"/>
+      <c r="F39" s="101"/>
+    </row>
+    <row r="40" spans="1:6" hidden="1">
+      <c r="A40" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="108"/>
+    </row>
+    <row r="41" spans="1:6" hidden="1">
+      <c r="A41" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" s="116"/>
+      <c r="D41" s="108"/>
+    </row>
+    <row r="42" spans="1:6" hidden="1">
+      <c r="A42" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C42" s="116"/>
+      <c r="D42" s="107"/>
+    </row>
+    <row r="43" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1">
+      <c r="A43" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B43" s="148"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="74">
+        <f>SUM(C39:C42)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" s="148"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="75"/>
+    </row>
+    <row r="45" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A45" s="85" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="70"/>
+      <c r="C45" s="116">
+        <v>123558.26</v>
+      </c>
+      <c r="D45" s="106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A46" s="70" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" s="70"/>
+      <c r="C46" s="116">
+        <v>282520.26</v>
+      </c>
+      <c r="D46" s="106" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="148"/>
-      <c r="C33" s="111">
-        <v>199000</v>
-      </c>
-      <c r="D33" s="109"/>
-      <c r="G33" s="12"/>
-    </row>
-    <row r="34" spans="1:7" ht="21" customHeight="1">
-      <c r="A34" s="149" t="s">
+    </row>
+    <row r="47" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A47" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="22"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="74">
+        <f>SUM(C45:C46)</f>
+        <v>406078.52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A48" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B48" s="22"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="77"/>
+    </row>
+    <row r="49" spans="1:6" ht="50.25" customHeight="1">
+      <c r="A49" s="157" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" s="158"/>
+      <c r="C49" s="116">
+        <v>210000</v>
+      </c>
+      <c r="D49" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="B34" s="150"/>
-      <c r="C34" s="111">
-        <v>80000</v>
-      </c>
-      <c r="D34" s="109"/>
-      <c r="G34" s="12"/>
-    </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1">
-      <c r="A35" s="22" t="s">
+    </row>
+    <row r="50" spans="1:6" ht="50.25" customHeight="1">
+      <c r="A50" s="157" t="s">
+        <v>122</v>
+      </c>
+      <c r="B50" s="158"/>
+      <c r="C50" s="116">
+        <v>387000</v>
+      </c>
+      <c r="D50" s="103" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="30" customHeight="1">
+      <c r="A51" s="181" t="s">
+        <v>113</v>
+      </c>
+      <c r="B51" s="182"/>
+      <c r="C51" s="116">
+        <v>10000</v>
+      </c>
+      <c r="D51" s="103" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A52" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="80">
+        <f>SUM(C49:C51)</f>
+        <v>607000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A53" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" s="149"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="77"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="70" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" s="70"/>
+      <c r="C54" s="118"/>
+      <c r="D54" s="81"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="70" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55" s="70"/>
+      <c r="C55" s="116">
+        <v>32988.99</v>
+      </c>
+      <c r="D55" s="79"/>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A56" s="150" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="72">
-        <f>SUM(C32:C34)</f>
-        <v>279000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="22"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="47"/>
-    </row>
-    <row r="37" spans="1:7" s="30" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A37" s="161" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" s="162"/>
-      <c r="C37" s="113">
-        <v>23077</v>
-      </c>
-      <c r="D37" s="108"/>
-    </row>
-    <row r="38" spans="1:7" ht="30" customHeight="1">
-      <c r="A38" s="161" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="162"/>
-      <c r="C38" s="114">
-        <v>141392</v>
-      </c>
-      <c r="D38" s="108"/>
-    </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1">
-      <c r="A39" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="74">
-        <f>SUM(C37:C38)</f>
-        <v>164469</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" hidden="1">
-      <c r="A40" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B40" s="152"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="75"/>
-    </row>
-    <row r="41" spans="1:7" hidden="1">
-      <c r="A41" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" s="70" t="s">
-        <v>119</v>
-      </c>
-      <c r="C41" s="115"/>
-      <c r="D41" s="108"/>
-      <c r="F41" s="101"/>
-    </row>
-    <row r="42" spans="1:7" hidden="1">
-      <c r="A42" s="70" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" s="70" t="s">
-        <v>119</v>
-      </c>
-      <c r="C42" s="116"/>
-      <c r="D42" s="108"/>
-    </row>
-    <row r="43" spans="1:7" hidden="1">
-      <c r="A43" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="B43" s="70" t="s">
-        <v>119</v>
-      </c>
-      <c r="C43" s="116"/>
-      <c r="D43" s="108"/>
-    </row>
-    <row r="44" spans="1:7" hidden="1">
-      <c r="A44" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="B44" s="70" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" s="116"/>
-      <c r="D44" s="107"/>
-    </row>
-    <row r="45" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1">
-      <c r="A45" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B45" s="152"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="74">
-        <f>SUM(C41:C44)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46" s="152"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="75"/>
-    </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A47" s="85" t="s">
-        <v>100</v>
-      </c>
-      <c r="B47" s="70"/>
-      <c r="C47" s="197">
-        <v>123558.26</v>
-      </c>
-      <c r="D47" s="106" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A48" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="B48" s="70"/>
-      <c r="C48" s="116"/>
-      <c r="D48" s="106"/>
-    </row>
-    <row r="49" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A49" s="70" t="s">
-        <v>101</v>
-      </c>
-      <c r="B49" s="70"/>
-      <c r="C49" s="197">
-        <v>354392.43</v>
-      </c>
-      <c r="D49" s="106" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15" thickBot="1">
-      <c r="A50" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B50" s="22"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="74">
-        <f>SUM(C47:C49)</f>
-        <v>477950.69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1">
-      <c r="A51" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B51" s="22"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="77"/>
-    </row>
-    <row r="52" spans="1:6" ht="30" customHeight="1">
-      <c r="A52" s="128" t="s">
-        <v>117</v>
-      </c>
-      <c r="B52" s="151"/>
-      <c r="C52" s="197">
-        <v>78900</v>
-      </c>
-      <c r="D52" s="103" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1">
-      <c r="A53" s="128" t="s">
-        <v>120</v>
-      </c>
-      <c r="B53" s="151"/>
-      <c r="C53" s="197">
-        <v>10000</v>
-      </c>
-      <c r="D53" s="103"/>
-    </row>
-    <row r="54" spans="1:6" ht="30" customHeight="1">
-      <c r="A54" s="128"/>
-      <c r="B54" s="151"/>
-      <c r="C54" s="116"/>
-      <c r="D54" s="103"/>
-    </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1">
-      <c r="A55" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="80">
-        <f>SUM(C52:C54)</f>
-        <v>88900</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1">
-      <c r="A56" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B56" s="153"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="77"/>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="70" t="s">
-        <v>69</v>
-      </c>
+      <c r="B56" s="150"/>
+      <c r="C56" s="82"/>
+      <c r="D56" s="74">
+        <f>SUM(C54:C55)</f>
+        <v>32988.99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A57" s="70"/>
       <c r="B57" s="70"/>
-      <c r="C57" s="118"/>
-      <c r="D57" s="81"/>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="70" t="s">
-        <v>111</v>
-      </c>
-      <c r="B58" s="70"/>
-      <c r="C58" s="116">
-        <v>6312.88</v>
-      </c>
-      <c r="D58" s="79"/>
-    </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1">
-      <c r="A59" s="154" t="s">
-        <v>29</v>
-      </c>
-      <c r="B59" s="154"/>
-      <c r="C59" s="82"/>
-      <c r="D59" s="74">
-        <f>SUM(C57:C58)</f>
-        <v>6312.88</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15" thickBot="1">
-      <c r="A60" s="70"/>
-      <c r="B60" s="70"/>
-      <c r="C60" s="70"/>
-      <c r="D60" s="83"/>
-    </row>
-    <row r="61" spans="1:6" ht="99" customHeight="1" thickBot="1">
-      <c r="A61" s="163" t="s">
-        <v>113</v>
-      </c>
-      <c r="B61" s="164"/>
-      <c r="C61" s="165"/>
-      <c r="D61" s="84">
-        <f>1800000-859687.59-199000</f>
-        <v>741312.41</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="15" thickBot="1">
-      <c r="A62" s="155"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="83"/>
+    </row>
+    <row r="58" spans="1:6" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A58" s="161" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" s="162"/>
+      <c r="C58" s="163"/>
+      <c r="D58" s="84"/>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A59" s="151"/>
+      <c r="B59" s="85"/>
+      <c r="C59" s="85"/>
+      <c r="D59" s="86"/>
+      <c r="E59" s="35"/>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A60" s="152" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" s="153"/>
+      <c r="C60" s="87"/>
+      <c r="D60" s="88">
+        <f>(SUM(D25:D58))</f>
+        <v>1406361.51</v>
+      </c>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="85"/>
+      <c r="B61" s="85"/>
+      <c r="C61" s="85"/>
+      <c r="D61" s="85"/>
+      <c r="F61" s="102"/>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A62" s="85"/>
       <c r="B62" s="85"/>
       <c r="C62" s="85"/>
-      <c r="D62" s="86"/>
-      <c r="E62" s="35"/>
-    </row>
-    <row r="63" spans="1:6" ht="15" thickBot="1">
-      <c r="A63" s="156" t="s">
-        <v>25</v>
-      </c>
-      <c r="B63" s="157"/>
-      <c r="C63" s="87"/>
-      <c r="D63" s="88">
-        <f>(SUM(D25:D61))</f>
-        <v>1889144.98</v>
-      </c>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
+      <c r="D62" s="85"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="154" t="s">
+        <v>34</v>
+      </c>
+      <c r="B63" s="155"/>
+      <c r="C63" s="89"/>
+      <c r="D63" s="90"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="85"/>
-      <c r="B64" s="85"/>
-      <c r="C64" s="85"/>
-      <c r="D64" s="85"/>
-      <c r="F64" s="102"/>
-    </row>
-    <row r="65" spans="1:4" ht="15" thickBot="1">
-      <c r="A65" s="85"/>
-      <c r="B65" s="85"/>
-      <c r="C65" s="85"/>
-      <c r="D65" s="85"/>
+      <c r="A64" s="157" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="158"/>
+      <c r="C64" s="78">
+        <v>11000</v>
+      </c>
+      <c r="D64" s="103" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="157"/>
+      <c r="B65" s="158"/>
+      <c r="C65" s="78"/>
+      <c r="D65" s="76"/>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="158" t="s">
-        <v>34</v>
-      </c>
-      <c r="B66" s="159"/>
-      <c r="C66" s="89"/>
-      <c r="D66" s="90"/>
+      <c r="A66" s="93"/>
+      <c r="B66" s="94"/>
+      <c r="C66" s="78"/>
+      <c r="D66" s="76"/>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="161"/>
-      <c r="B67" s="162"/>
-      <c r="C67" s="78"/>
-      <c r="D67" s="76"/>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="161"/>
-      <c r="B68" s="162"/>
-      <c r="C68" s="78"/>
-      <c r="D68" s="76"/>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="93"/>
-      <c r="B69" s="94"/>
-      <c r="C69" s="78"/>
-      <c r="D69" s="76"/>
-    </row>
+      <c r="A67" s="38"/>
+      <c r="B67" s="37"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="42">
+        <f>SUM(C64:C66)</f>
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15" customHeight="1"/>
+    <row r="69" spans="1:4" hidden="1"/>
     <row r="70" spans="1:4">
-      <c r="A70" s="38"/>
-      <c r="B70" s="37"/>
-      <c r="C70" s="42"/>
-      <c r="D70" s="42">
-        <f>SUM(C67:C69)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="15" customHeight="1"/>
-    <row r="72" spans="1:4" hidden="1"/>
-    <row r="73" spans="1:4">
-      <c r="A73" s="17" t="s">
+      <c r="A70" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B73" s="17"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="15" thickBot="1"/>
-    <row r="75" spans="1:4" ht="15" thickBot="1">
-      <c r="A75" s="2" t="s">
+      <c r="B70" s="17"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" thickBot="1"/>
+    <row r="72" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A72" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B75" s="8"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="48">
-        <f>D70+D73</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1"/>
-    <row r="77" spans="1:4" ht="15" thickBot="1">
+      <c r="B72" s="8"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="48">
+        <f>D67+D70</f>
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" thickBot="1"/>
+    <row r="74" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A74" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="B74" s="69">
+        <f>D60</f>
+        <v>1406361.51</v>
+      </c>
+      <c r="C74" s="35"/>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A75" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75" s="69">
+        <f>D60-D58</f>
+        <v>1406361.51</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A76" s="68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="69">
+        <f>D72-D70</f>
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15.75" thickBot="1">
       <c r="A77" s="68" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B77" s="69">
-        <f>D63</f>
-        <v>1889144.98</v>
-      </c>
-      <c r="C77" s="35"/>
-    </row>
-    <row r="78" spans="1:4" ht="15" thickBot="1">
-      <c r="A78" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="B78" s="69">
-        <f>D63-D61</f>
-        <v>1147832.5699999998</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="15" thickBot="1">
-      <c r="A79" s="68" t="s">
-        <v>37</v>
-      </c>
-      <c r="B79" s="69">
-        <f>D75-D73</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="15" thickBot="1">
-      <c r="A80" s="68" t="s">
-        <v>52</v>
-      </c>
-      <c r="B80" s="69">
-        <f>D75</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="15" thickBot="1">
-      <c r="A84" s="13" t="s">
+        <f>D72</f>
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="B80" s="192"/>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="192"/>
+      <c r="B81" s="192"/>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="192"/>
+      <c r="B82" s="192"/>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="192"/>
+      <c r="B83" s="192"/>
+    </row>
+    <row r="87" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A87" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B84" s="127"/>
-    </row>
-    <row r="85" spans="1:3" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A85" s="20" t="s">
+      <c r="B87" s="127"/>
+    </row>
+    <row r="88" spans="1:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A88" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B85" s="129">
-        <v>-169461</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A86" s="14" t="s">
+      <c r="B88" s="191">
+        <v>159602.50000000023</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A89" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B86" s="32">
-        <f>PRORRATEO!H27</f>
-        <v>1387751.09</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A87" s="14" t="s">
+      <c r="B89" s="32">
+        <f>PRORRATEO!H24</f>
+        <v>2022091.92</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A90" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B87" s="79">
-        <f>B97</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="13.95" customHeight="1">
-      <c r="A88" s="15" t="s">
+      <c r="B90" s="79">
+        <f>B102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="13.9" customHeight="1">
+      <c r="A91" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B88" s="105"/>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="31" t="s">
+      <c r="B91" s="105"/>
+    </row>
+    <row r="92" spans="1:3" ht="65.25" customHeight="1">
+      <c r="A92" s="194" t="s">
+        <v>119</v>
+      </c>
+      <c r="B92" s="189">
+        <v>-480000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="13.9" customHeight="1">
+      <c r="A93" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B93" s="79">
+        <f>141260.13+61769.13</f>
+        <v>203029.26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B89" s="105">
-        <f>-B78</f>
-        <v>-1147832.5699999998</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="15" t="s">
+      <c r="B94" s="105">
+        <f>-B75</f>
+        <v>-1406361.51</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B90" s="79">
-        <f>-(B79)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="19" t="s">
+      <c r="B95" s="79">
+        <f>-(B76)</f>
+        <v>-11000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B91" s="130">
-        <f>SUM(B85:B90)</f>
-        <v>70457.520000000251</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="34.5" customHeight="1">
-      <c r="B92" s="33"/>
-      <c r="C92" s="35"/>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="160" t="s">
+      <c r="B96" s="129">
+        <f>SUM(B88:B95)</f>
+        <v>487362.16999999993</v>
+      </c>
+      <c r="C96" s="190"/>
+    </row>
+    <row r="97" spans="1:12" ht="34.5" customHeight="1">
+      <c r="B97" s="33"/>
+      <c r="C97" s="35"/>
+      <c r="D97" s="190"/>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" s="160" t="s">
         <v>46</v>
       </c>
-      <c r="B93" s="160"/>
-    </row>
-    <row r="94" spans="1:3" ht="27.75" customHeight="1">
-      <c r="A94" s="160"/>
-      <c r="B94" s="160"/>
-    </row>
-    <row r="95" spans="1:3" ht="32.25" customHeight="1">
-      <c r="A95" s="91"/>
-      <c r="B95" s="26"/>
-    </row>
-    <row r="96" spans="1:3" ht="32.25" customHeight="1">
-      <c r="A96" s="91"/>
-      <c r="B96" s="26"/>
-    </row>
-    <row r="97" spans="1:12">
-      <c r="A97" s="36" t="s">
+      <c r="B98" s="160"/>
+    </row>
+    <row r="99" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A99" s="160"/>
+      <c r="B99" s="160"/>
+    </row>
+    <row r="100" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A100" s="91"/>
+      <c r="B100" s="26"/>
+    </row>
+    <row r="101" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A101" s="91"/>
+      <c r="B101" s="26"/>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B97" s="92">
-        <f>SUM(B95:B96)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12">
-      <c r="L98" s="6"/>
+      <c r="B102" s="92">
+        <f>SUM(B100:B101)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="L103" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="13">
     <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A93:B94"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A98:B99"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A80:B83"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2931,377 +2941,533 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:U32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.9" customHeight="1">
-      <c r="A1" s="131"/>
-      <c r="B1" s="173" t="str">
+    <row r="1" spans="1:21" ht="12.95" customHeight="1">
+      <c r="A1" s="130"/>
+      <c r="B1" s="165" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="133"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="132"/>
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
-      <c r="A2" s="134"/>
-      <c r="B2" s="174"/>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135" t="s">
+      <c r="A2" s="133"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
+      <c r="L2" s="134"/>
+      <c r="M2" s="134" t="s">
         <v>4</v>
       </c>
       <c r="N2" s="5"/>
-      <c r="O2" s="143">
-        <v>1800000</v>
-      </c>
-      <c r="P2" s="136"/>
+      <c r="O2" s="142">
+        <f>R2</f>
+        <v>1406361.51</v>
+      </c>
+      <c r="P2" s="135"/>
       <c r="Q2" s="12"/>
+      <c r="R2">
+        <v>1406361.51</v>
+      </c>
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
-      <c r="A3" s="137"/>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
-      <c r="L3" s="138"/>
-      <c r="M3" s="138" t="s">
+      <c r="A3" s="136"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="167"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="167"/>
+      <c r="I3" s="167"/>
+      <c r="J3" s="167"/>
+      <c r="K3" s="167"/>
+      <c r="L3" s="137"/>
+      <c r="M3" s="137" t="s">
         <v>56</v>
       </c>
-      <c r="N3" s="139"/>
-      <c r="O3" s="144"/>
-      <c r="P3" s="140"/>
+      <c r="N3" s="138"/>
+      <c r="O3" s="143">
+        <v>11000</v>
+      </c>
+      <c r="P3" s="139"/>
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="5"/>
-      <c r="B4" s="185" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
-      <c r="M4" s="186"/>
-      <c r="N4" s="186"/>
-      <c r="O4" s="186"/>
-      <c r="P4" s="187"/>
-    </row>
-    <row r="5" spans="1:21" ht="30.6" customHeight="1">
-      <c r="A5" s="5"/>
-      <c r="B5" s="188" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="189"/>
-      <c r="D5" s="189"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="189"/>
-      <c r="H5" s="189"/>
-      <c r="I5" s="189"/>
-      <c r="J5" s="189"/>
-      <c r="K5" s="189"/>
-      <c r="L5" s="189"/>
-      <c r="M5" s="189"/>
-      <c r="N5" s="189"/>
-      <c r="O5" s="189"/>
-      <c r="P5" s="190"/>
-    </row>
-    <row r="6" spans="1:21" ht="30.6" customHeight="1">
-      <c r="A6" s="5"/>
-      <c r="B6" s="191"/>
-      <c r="C6" s="192"/>
-      <c r="D6" s="192"/>
-      <c r="E6" s="192"/>
-      <c r="F6" s="192"/>
-      <c r="G6" s="192"/>
-      <c r="H6" s="192"/>
-      <c r="I6" s="192"/>
-      <c r="J6" s="192"/>
-      <c r="K6" s="192"/>
-      <c r="L6" s="192"/>
-      <c r="M6" s="192"/>
-      <c r="N6" s="192"/>
-      <c r="O6" s="192"/>
-      <c r="P6" s="193"/>
-    </row>
-    <row r="7" spans="1:21" ht="155.25" customHeight="1" thickBot="1">
-      <c r="A7" s="5"/>
-      <c r="B7" s="194"/>
-      <c r="C7" s="195"/>
-      <c r="D7" s="195"/>
-      <c r="E7" s="195"/>
-      <c r="F7" s="195"/>
-      <c r="G7" s="195"/>
-      <c r="H7" s="195"/>
-      <c r="I7" s="195"/>
-      <c r="J7" s="195"/>
-      <c r="K7" s="195"/>
-      <c r="L7" s="195"/>
-      <c r="M7" s="195"/>
-      <c r="N7" s="195"/>
-      <c r="O7" s="195"/>
-      <c r="P7" s="196"/>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="169" t="s">
+      <c r="B4" s="183" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="184"/>
+      <c r="D4" s="184"/>
+      <c r="E4" s="184"/>
+      <c r="F4" s="184"/>
+      <c r="G4" s="184"/>
+      <c r="H4" s="184"/>
+      <c r="I4" s="184"/>
+      <c r="J4" s="184"/>
+      <c r="K4" s="184"/>
+      <c r="L4" s="184"/>
+      <c r="M4" s="184"/>
+      <c r="N4" s="184"/>
+      <c r="O4" s="184"/>
+      <c r="P4" s="185"/>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="178" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="171" t="s">
+      <c r="B5" s="180" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="172" t="s">
+      <c r="C5" s="170" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="172" t="s">
+      <c r="D5" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="172" t="s">
+      <c r="E5" s="170" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="172" t="s">
+      <c r="F5" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="172" t="s">
+      <c r="G5" s="170" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="172" t="s">
+      <c r="H5" s="170" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="172" t="s">
+      <c r="I5" s="170" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="181" t="s">
+      <c r="J5" s="174" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="179" t="s">
+      <c r="K5" s="172" t="s">
         <v>41</v>
       </c>
-      <c r="L8" s="179" t="s">
+      <c r="L5" s="172" t="s">
         <v>10</v>
       </c>
-      <c r="M8" s="179" t="s">
+      <c r="M5" s="172" t="s">
         <v>40</v>
       </c>
-      <c r="N8" s="183" t="s">
+      <c r="N5" s="176" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="117" t="s">
+      <c r="O5" s="117" t="s">
         <v>50</v>
       </c>
-      <c r="P8" s="176" t="s">
+      <c r="P5" s="168" t="s">
         <v>49</v>
       </c>
-      <c r="S8" s="35"/>
-      <c r="T8" s="33"/>
-    </row>
-    <row r="9" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A9" s="170"/>
-      <c r="B9" s="171"/>
-      <c r="C9" s="172"/>
-      <c r="D9" s="172"/>
-      <c r="E9" s="178"/>
-      <c r="F9" s="172"/>
-      <c r="G9" s="172"/>
-      <c r="H9" s="172"/>
-      <c r="I9" s="178"/>
-      <c r="J9" s="182"/>
-      <c r="K9" s="180"/>
-      <c r="L9" s="179"/>
-      <c r="M9" s="180"/>
-      <c r="N9" s="184"/>
-      <c r="O9" s="43" t="str">
+      <c r="S5" s="35"/>
+      <c r="T5" s="33"/>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A6" s="179"/>
+      <c r="B6" s="180"/>
+      <c r="C6" s="170"/>
+      <c r="D6" s="170"/>
+      <c r="E6" s="171"/>
+      <c r="F6" s="170"/>
+      <c r="G6" s="170"/>
+      <c r="H6" s="170"/>
+      <c r="I6" s="171"/>
+      <c r="J6" s="175"/>
+      <c r="K6" s="173"/>
+      <c r="L6" s="172"/>
+      <c r="M6" s="173"/>
+      <c r="N6" s="177"/>
+      <c r="O6" s="43" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/02</v>
       </c>
-      <c r="P9" s="176"/>
+      <c r="P6" s="168"/>
+      <c r="S6" s="33">
+        <v>65160</v>
+      </c>
+      <c r="T6" s="33">
+        <v>157470</v>
+      </c>
+      <c r="U6" s="35">
+        <f>T6+S6</f>
+        <v>222630</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="45">
+        <v>1</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="45"/>
+      <c r="F7" s="49">
+        <v>10.86</v>
+      </c>
+      <c r="G7" s="50">
+        <v>2997197.01</v>
+      </c>
+      <c r="H7" s="51"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="53">
+        <f>G7-H7</f>
+        <v>2997197.01</v>
+      </c>
+      <c r="K7" s="53">
+        <f>IF(J7&gt;0,J7*3%,0)</f>
+        <v>89915.910299999989</v>
+      </c>
+      <c r="L7" s="54">
+        <f>O$3*F7%</f>
+        <v>1194.5999999999999</v>
+      </c>
+      <c r="M7" s="54">
+        <f>O$2*F7%</f>
+        <v>152730.859986</v>
+      </c>
+      <c r="N7" s="55">
+        <v>0</v>
+      </c>
+      <c r="O7" s="56">
+        <f>ROUND(SUM(J7:N7),0) + Q7</f>
+        <v>3241038.01</v>
+      </c>
+      <c r="P7" s="57">
+        <f t="shared" ref="P7:P23" si="0">ROUND(O7*3%,0) + O7</f>
+        <v>3338269.01</v>
+      </c>
+      <c r="Q7" s="35">
+        <v>0.01</v>
+      </c>
+      <c r="S7" s="33">
+        <v>66960</v>
+      </c>
+      <c r="T7" s="33">
+        <v>161820</v>
+      </c>
+      <c r="U7" s="35">
+        <f t="shared" ref="U7:U21" si="1">T7+S7</f>
+        <v>228780</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="45">
+        <v>2</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="46"/>
+      <c r="F8" s="49">
+        <v>11.16</v>
+      </c>
+      <c r="G8" s="50">
+        <v>207261.02</v>
+      </c>
+      <c r="H8" s="51">
+        <f>217829.14-H18</f>
+        <v>207261.02000000002</v>
+      </c>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53">
+        <f t="shared" ref="J8:J22" si="2">G8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="53">
+        <f t="shared" ref="K8:K22" si="3">IF(J8&gt;0,J8*3%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="54">
+        <f t="shared" ref="L8:L23" si="4">O$3*F8%</f>
+        <v>1227.6000000000001</v>
+      </c>
+      <c r="M8" s="54">
+        <f t="shared" ref="M8:M23" si="5">O$2*F8%</f>
+        <v>156949.94451600002</v>
+      </c>
+      <c r="N8" s="55">
+        <v>0</v>
+      </c>
+      <c r="O8" s="56">
+        <f>ROUND(SUM(J8:N8),0) + Q8</f>
+        <v>158178.01999999999</v>
+      </c>
+      <c r="P8" s="57">
+        <f t="shared" si="0"/>
+        <v>162923.01999999999</v>
+      </c>
+      <c r="Q8" s="35">
+        <f>Q7+0.01</f>
+        <v>0.02</v>
+      </c>
+      <c r="R8" s="35"/>
+      <c r="S8" s="33">
+        <v>41700</v>
+      </c>
+      <c r="T8" s="33">
+        <v>100775</v>
+      </c>
+      <c r="U8" s="35">
+        <f t="shared" si="1"/>
+        <v>142475</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="104">
+        <v>4</v>
+      </c>
+      <c r="C9" s="104" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="119" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="187" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" s="121">
+        <v>6.95</v>
+      </c>
+      <c r="G9" s="51">
+        <v>147207.03</v>
+      </c>
+      <c r="H9" s="51">
+        <v>100775</v>
+      </c>
+      <c r="I9" s="52"/>
+      <c r="J9" s="122">
+        <f t="shared" si="2"/>
+        <v>46432.03</v>
+      </c>
+      <c r="K9" s="53">
+        <f t="shared" si="3"/>
+        <v>1392.9608999999998</v>
+      </c>
+      <c r="L9" s="123">
+        <f t="shared" si="4"/>
+        <v>764.50000000000011</v>
+      </c>
+      <c r="M9" s="123">
+        <f t="shared" si="5"/>
+        <v>97742.124945000003</v>
+      </c>
+      <c r="N9" s="124">
+        <v>0</v>
+      </c>
+      <c r="O9" s="125">
+        <f t="shared" ref="O9:O23" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
+        <v>146332.03</v>
+      </c>
+      <c r="P9" s="126">
+        <f t="shared" si="0"/>
+        <v>150722.03</v>
+      </c>
+      <c r="Q9" s="35">
+        <f t="shared" ref="Q9:Q22" si="7">Q8+0.01</f>
+        <v>0.03</v>
+      </c>
       <c r="S9" s="33">
-        <v>65160</v>
+        <v>44220</v>
       </c>
       <c r="T9" s="33">
-        <v>157470</v>
+        <v>106865</v>
       </c>
       <c r="U9" s="35">
-        <f>T9+S9</f>
-        <v>222630</v>
+        <f t="shared" si="1"/>
+        <v>151085</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B10" s="45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D10" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="45"/>
+        <v>89</v>
+      </c>
+      <c r="E10" s="186" t="s">
+        <v>125</v>
+      </c>
       <c r="F10" s="49">
-        <v>10.86</v>
+        <v>7.37</v>
       </c>
       <c r="G10" s="50">
-        <v>2720114.01</v>
-      </c>
-      <c r="H10" s="51"/>
+        <v>288278.03999999998</v>
+      </c>
+      <c r="H10" s="51">
+        <f>297919-H20</f>
+        <v>288558.86</v>
+      </c>
       <c r="I10" s="52"/>
       <c r="J10" s="53">
-        <f>G10-H10</f>
-        <v>2720114.01</v>
+        <f t="shared" si="2"/>
+        <v>-280.82000000000698</v>
       </c>
       <c r="K10" s="53">
-        <f>IF(J10&gt;0,J10*3%,0)</f>
-        <v>81603.420299999983</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="L10" s="54">
-        <f>O$3*F10%</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>810.7</v>
       </c>
       <c r="M10" s="54">
-        <f>O$2*F10%</f>
-        <v>195479.99999999997</v>
+        <f t="shared" si="5"/>
+        <v>103648.843287</v>
       </c>
       <c r="N10" s="55">
         <v>0</v>
       </c>
       <c r="O10" s="56">
-        <f>ROUND(SUM(J10:N10),0) + Q10</f>
-        <v>2997197.01</v>
+        <f t="shared" si="6"/>
+        <v>104179.04</v>
       </c>
       <c r="P10" s="57">
-        <f t="shared" ref="P10:P26" si="0">ROUND(O10*3%,0) + O10</f>
-        <v>3087113.01</v>
+        <f t="shared" si="0"/>
+        <v>107304.04</v>
       </c>
       <c r="Q10" s="35">
-        <v>0.01</v>
+        <f t="shared" si="7"/>
+        <v>0.04</v>
       </c>
       <c r="S10" s="33">
-        <v>66960</v>
+        <v>64080</v>
       </c>
       <c r="T10" s="33">
-        <v>161820</v>
+        <v>154860</v>
       </c>
       <c r="U10" s="35">
-        <f t="shared" ref="U10:U24" si="1">T10+S10</f>
-        <v>228780</v>
+        <f t="shared" si="1"/>
+        <v>218940</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="46"/>
+        <v>90</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>107</v>
+      </c>
       <c r="F11" s="49">
-        <v>11.16</v>
+        <v>10.68</v>
       </c>
       <c r="G11" s="50">
-        <v>228780</v>
+        <v>192240.05</v>
       </c>
       <c r="H11" s="51">
-        <f>240131-H21</f>
-        <v>228446</v>
+        <f>G11</f>
+        <v>192240.05</v>
       </c>
       <c r="I11" s="52"/>
       <c r="J11" s="53">
-        <f t="shared" ref="J11:J25" si="2">G11-H11</f>
-        <v>334</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K11" s="53">
-        <f t="shared" ref="K11:K25" si="3">IF(J11&gt;0,J11*3%,0)</f>
-        <v>10.02</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="L11" s="54">
-        <f t="shared" ref="L11:L26" si="4">O$3*F11%</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1174.8</v>
       </c>
       <c r="M11" s="54">
-        <f t="shared" ref="M11:M26" si="5">O$2*F11%</f>
-        <v>200880</v>
+        <f t="shared" si="5"/>
+        <v>150199.40926799999</v>
       </c>
       <c r="N11" s="55">
         <v>0</v>
       </c>
       <c r="O11" s="56">
-        <f>ROUND(SUM(J11:N11),0) + Q11</f>
-        <v>201224.02</v>
+        <f t="shared" si="6"/>
+        <v>151374.04999999999</v>
       </c>
       <c r="P11" s="57">
         <f t="shared" si="0"/>
-        <v>207261.02</v>
+        <v>155915.04999999999</v>
       </c>
       <c r="Q11" s="35">
-        <f>Q10+0.01</f>
-        <v>0.02</v>
-      </c>
-      <c r="R11" s="35"/>
+        <f t="shared" si="7"/>
+        <v>0.05</v>
+      </c>
       <c r="S11" s="33">
         <v>41700</v>
       </c>
@@ -3315,125 +3481,133 @@
     </row>
     <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="104">
-        <v>4</v>
-      </c>
-      <c r="C12" s="104" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="119" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="120"/>
-      <c r="F12" s="121">
+        <v>15</v>
+      </c>
+      <c r="B12" s="45">
+        <v>7</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="49">
         <v>6.95</v>
       </c>
-      <c r="G12" s="51">
-        <v>142475</v>
+      <c r="G12" s="50">
+        <v>125100.06</v>
       </c>
       <c r="H12" s="51">
-        <f>74400+50775</f>
-        <v>125175</v>
+        <f>136080-H22</f>
+        <v>125099.84</v>
       </c>
       <c r="I12" s="52"/>
-      <c r="J12" s="122">
+      <c r="J12" s="53">
         <f t="shared" si="2"/>
-        <v>17300</v>
+        <v>0.22000000000116415</v>
       </c>
       <c r="K12" s="53">
         <f t="shared" si="3"/>
-        <v>519</v>
-      </c>
-      <c r="L12" s="123">
+        <v>6.6000000000349243E-3</v>
+      </c>
+      <c r="L12" s="54">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="123">
+        <v>764.50000000000011</v>
+      </c>
+      <c r="M12" s="54">
         <f t="shared" si="5"/>
-        <v>125100.00000000001</v>
-      </c>
-      <c r="N12" s="124">
-        <v>0</v>
-      </c>
-      <c r="O12" s="125">
-        <f t="shared" ref="O12:O26" si="6">ROUND(SUM(J12:N12),0) + Q12</f>
-        <v>142919.03</v>
-      </c>
-      <c r="P12" s="126">
+        <v>97742.124945000003</v>
+      </c>
+      <c r="N12" s="188">
+        <v>480000</v>
+      </c>
+      <c r="O12" s="56">
+        <f>ROUND(SUM(J12:N12),0) + Q12</f>
+        <v>578507.06000000006</v>
+      </c>
+      <c r="P12" s="57">
         <f t="shared" si="0"/>
-        <v>147207.03</v>
+        <v>595862.06000000006</v>
       </c>
       <c r="Q12" s="35">
-        <f t="shared" ref="Q12:Q25" si="7">Q11+0.01</f>
-        <v>0.03</v>
+        <f t="shared" si="7"/>
+        <v>6.0000000000000005E-2</v>
       </c>
       <c r="S12" s="33">
-        <v>44220</v>
+        <v>41340</v>
       </c>
       <c r="T12" s="33">
-        <v>106865</v>
+        <v>99905</v>
       </c>
       <c r="U12" s="35">
         <f t="shared" si="1"/>
-        <v>151085</v>
+        <v>141245</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="45">
-        <v>3</v>
-      </c>
-      <c r="C13" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="46"/>
+        <v>6</v>
+      </c>
+      <c r="C13" s="104" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="104" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>108</v>
+      </c>
       <c r="F13" s="49">
-        <v>7.37</v>
+        <v>6.89</v>
       </c>
       <c r="G13" s="50">
-        <v>151085</v>
-      </c>
-      <c r="H13" s="51"/>
+        <v>124020.07</v>
+      </c>
+      <c r="H13" s="51">
+        <f>G13</f>
+        <v>124020.07</v>
+      </c>
       <c r="I13" s="52"/>
       <c r="J13" s="53">
         <f t="shared" si="2"/>
-        <v>151085</v>
+        <v>0</v>
       </c>
       <c r="K13" s="53">
         <f t="shared" si="3"/>
-        <v>4532.55</v>
+        <v>0</v>
       </c>
       <c r="L13" s="54">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>757.9</v>
       </c>
       <c r="M13" s="54">
         <f t="shared" si="5"/>
-        <v>132660</v>
+        <v>96898.30803900001</v>
       </c>
       <c r="N13" s="55">
         <v>0</v>
       </c>
       <c r="O13" s="56">
         <f t="shared" si="6"/>
-        <v>288278.03999999998</v>
+        <v>97656.07</v>
       </c>
       <c r="P13" s="57">
         <f t="shared" si="0"/>
-        <v>296926.03999999998</v>
+        <v>100586.07</v>
       </c>
       <c r="Q13" s="35">
         <f t="shared" si="7"/>
-        <v>0.04</v>
-      </c>
-      <c r="S13" s="33">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="R13" s="102"/>
+      <c r="S13" s="140">
         <v>64080</v>
       </c>
       <c r="T13" s="33">
@@ -3446,29 +3620,29 @@
     </row>
     <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="45">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>109</v>
+        <v>92</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>106</v>
       </c>
       <c r="F14" s="49">
         <v>10.68</v>
       </c>
       <c r="G14" s="50">
-        <v>218940</v>
+        <v>192240.08</v>
       </c>
       <c r="H14" s="51">
         <f>G14</f>
-        <v>218940</v>
+        <v>192240.08</v>
       </c>
       <c r="I14" s="52"/>
       <c r="J14" s="53">
@@ -3481,26 +3655,26 @@
       </c>
       <c r="L14" s="54">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1174.8</v>
       </c>
       <c r="M14" s="54">
         <f t="shared" si="5"/>
-        <v>192240</v>
+        <v>150199.40926799999</v>
       </c>
       <c r="N14" s="55">
         <v>0</v>
       </c>
       <c r="O14" s="56">
         <f t="shared" si="6"/>
-        <v>192240.05</v>
+        <v>151374.07999999999</v>
       </c>
       <c r="P14" s="57">
         <f t="shared" si="0"/>
-        <v>198007.05</v>
+        <v>155915.07999999999</v>
       </c>
       <c r="Q14" s="35">
         <f t="shared" si="7"/>
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="S14" s="33">
         <v>41700</v>
@@ -3515,59 +3689,59 @@
     </row>
     <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="45">
-        <v>7</v>
-      </c>
-      <c r="C15" s="45" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" s="45"/>
-      <c r="F15" s="49">
+        <v>16</v>
+      </c>
+      <c r="B15" s="104">
+        <v>10</v>
+      </c>
+      <c r="C15" s="104" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="104" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="120"/>
+      <c r="F15" s="121">
         <v>6.95</v>
       </c>
-      <c r="G15" s="50">
-        <v>142475</v>
-      </c>
-      <c r="H15" s="51">
-        <f>154980-H25</f>
-        <v>142475</v>
+      <c r="G15" s="51">
+        <v>142301.09</v>
+      </c>
+      <c r="H15" s="141">
+        <f>G15</f>
+        <v>142301.09</v>
       </c>
       <c r="I15" s="52"/>
-      <c r="J15" s="53">
+      <c r="J15" s="122">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K15" s="53">
+      <c r="K15" s="122">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L15" s="54">
+      <c r="L15" s="123">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="54">
+        <v>764.50000000000011</v>
+      </c>
+      <c r="M15" s="123">
         <f t="shared" si="5"/>
-        <v>125100.00000000001</v>
-      </c>
-      <c r="N15" s="55">
-        <v>0</v>
-      </c>
-      <c r="O15" s="56">
+        <v>97742.124945000003</v>
+      </c>
+      <c r="N15" s="124">
+        <v>0</v>
+      </c>
+      <c r="O15" s="125">
         <f t="shared" si="6"/>
-        <v>125100.06</v>
-      </c>
-      <c r="P15" s="57">
+        <v>98507.09</v>
+      </c>
+      <c r="P15" s="126">
         <f t="shared" si="0"/>
-        <v>128853.06</v>
+        <v>101462.09</v>
       </c>
       <c r="Q15" s="35">
         <f t="shared" si="7"/>
-        <v>6.0000000000000005E-2</v>
+        <v>0.09</v>
       </c>
       <c r="S15" s="33">
         <v>41340</v>
@@ -3582,29 +3756,29 @@
     </row>
     <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" s="45">
-        <v>6</v>
-      </c>
-      <c r="C16" s="104" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="104" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>110</v>
+        <v>9</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>105</v>
       </c>
       <c r="F16" s="49">
         <v>6.89</v>
       </c>
       <c r="G16" s="50">
-        <v>141245</v>
+        <v>124020.1</v>
       </c>
       <c r="H16" s="51">
         <f>G16</f>
-        <v>141245</v>
+        <v>124020.1</v>
       </c>
       <c r="I16" s="52"/>
       <c r="J16" s="53">
@@ -3617,64 +3791,61 @@
       </c>
       <c r="L16" s="54">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>757.9</v>
       </c>
       <c r="M16" s="54">
         <f t="shared" si="5"/>
-        <v>124020</v>
+        <v>96898.30803900001</v>
       </c>
       <c r="N16" s="55">
         <v>0</v>
       </c>
       <c r="O16" s="56">
         <f t="shared" si="6"/>
-        <v>124020.07</v>
+        <v>97656.1</v>
       </c>
       <c r="P16" s="57">
         <f t="shared" si="0"/>
-        <v>127741.07</v>
+        <v>100586.1</v>
       </c>
       <c r="Q16" s="35">
         <f t="shared" si="7"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="R16" s="102"/>
-      <c r="S16" s="141">
-        <v>64080</v>
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="S16" s="33">
+        <v>71280</v>
       </c>
       <c r="T16" s="33">
-        <v>154860</v>
+        <v>172260</v>
       </c>
       <c r="U16" s="35">
         <f t="shared" si="1"/>
-        <v>218940</v>
+        <v>243540</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="45">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D17" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="45" t="s">
-        <v>108</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="E17" s="46"/>
       <c r="F17" s="49">
-        <v>10.68</v>
+        <v>11.88</v>
       </c>
       <c r="G17" s="50">
-        <v>218940</v>
+        <v>464686.11</v>
       </c>
       <c r="H17" s="51">
         <f>G17</f>
-        <v>218940</v>
+        <v>464686.11</v>
       </c>
       <c r="I17" s="52"/>
       <c r="J17" s="53">
@@ -3687,135 +3858,132 @@
       </c>
       <c r="L17" s="54">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1306.8</v>
       </c>
       <c r="M17" s="54">
         <f t="shared" si="5"/>
-        <v>192240</v>
+        <v>167075.74738800002</v>
       </c>
       <c r="N17" s="55">
         <v>0</v>
       </c>
       <c r="O17" s="56">
         <f t="shared" si="6"/>
-        <v>192240.08</v>
+        <v>168383.11</v>
       </c>
       <c r="P17" s="57">
         <f t="shared" si="0"/>
-        <v>198007.08</v>
+        <v>173434.11</v>
       </c>
       <c r="Q17" s="35">
         <f t="shared" si="7"/>
-        <v>0.08</v>
+        <v>0.10999999999999999</v>
       </c>
       <c r="S17" s="33">
-        <v>41700</v>
+        <v>3420</v>
       </c>
       <c r="T17" s="33">
-        <v>100775</v>
+        <v>8265</v>
       </c>
       <c r="U17" s="35">
         <f t="shared" si="1"/>
-        <v>142475</v>
+        <v>11685</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="104">
-        <v>10</v>
-      </c>
-      <c r="C18" s="104" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="120"/>
-      <c r="F18" s="121">
-        <v>6.95</v>
-      </c>
-      <c r="G18" s="51">
-        <v>142475</v>
-      </c>
-      <c r="H18" s="142">
-        <f>41700+84075.09</f>
-        <v>125775.09</v>
+        <v>18</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="46"/>
+      <c r="F18" s="49">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G18" s="50">
+        <v>10568.12</v>
+      </c>
+      <c r="H18" s="51">
+        <f>G18</f>
+        <v>10568.12</v>
       </c>
       <c r="I18" s="52"/>
-      <c r="J18" s="122">
+      <c r="J18" s="53">
         <f t="shared" si="2"/>
-        <v>16699.910000000003</v>
-      </c>
-      <c r="K18" s="122">
+        <v>0</v>
+      </c>
+      <c r="K18" s="53">
         <f t="shared" si="3"/>
-        <v>500.99730000000011</v>
-      </c>
-      <c r="L18" s="123">
+        <v>0</v>
+      </c>
+      <c r="L18" s="54">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="123">
+        <v>62.699999999999996</v>
+      </c>
+      <c r="M18" s="54">
         <f t="shared" si="5"/>
-        <v>125100.00000000001</v>
-      </c>
-      <c r="N18" s="124">
-        <v>0</v>
-      </c>
-      <c r="O18" s="125">
+        <v>8016.2606069999993</v>
+      </c>
+      <c r="N18" s="55">
+        <v>0</v>
+      </c>
+      <c r="O18" s="56">
         <f t="shared" si="6"/>
-        <v>142301.09</v>
-      </c>
-      <c r="P18" s="126">
+        <v>8079.12</v>
+      </c>
+      <c r="P18" s="57">
         <f t="shared" si="0"/>
-        <v>146570.09</v>
+        <v>8321.119999999999</v>
       </c>
       <c r="Q18" s="35">
         <f t="shared" si="7"/>
-        <v>0.09</v>
+        <v>0.11999999999999998</v>
       </c>
       <c r="S18" s="33">
-        <v>41340</v>
+        <v>3120</v>
       </c>
       <c r="T18" s="33">
-        <v>99905</v>
+        <v>7540</v>
       </c>
       <c r="U18" s="35">
         <f t="shared" si="1"/>
-        <v>141245</v>
+        <v>10660</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="45">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>69</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D19" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="46" t="s">
-        <v>107</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="E19" s="46"/>
       <c r="F19" s="49">
-        <v>6.89</v>
+        <v>0.52</v>
       </c>
       <c r="G19" s="50">
-        <v>141245</v>
+        <v>9360.1299999999992</v>
       </c>
       <c r="H19" s="51">
-        <f>G19</f>
-        <v>141245</v>
+        <v>9641.1299999999992</v>
       </c>
       <c r="I19" s="52"/>
       <c r="J19" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-281</v>
       </c>
       <c r="K19" s="53">
         <f t="shared" si="3"/>
@@ -3823,125 +3991,130 @@
       </c>
       <c r="L19" s="54">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>57.199999999999996</v>
       </c>
       <c r="M19" s="54">
         <f t="shared" si="5"/>
-        <v>124020</v>
+        <v>7313.0798519999998</v>
       </c>
       <c r="N19" s="55">
         <v>0</v>
       </c>
       <c r="O19" s="56">
         <f t="shared" si="6"/>
-        <v>124020.1</v>
+        <v>7089.13</v>
       </c>
       <c r="P19" s="57">
         <f t="shared" si="0"/>
-        <v>127741.1</v>
+        <v>7302.13</v>
       </c>
       <c r="Q19" s="35">
         <f t="shared" si="7"/>
-        <v>9.9999999999999992E-2</v>
+        <v>0.12999999999999998</v>
       </c>
       <c r="S19" s="33">
-        <v>71280</v>
+        <v>3120</v>
       </c>
       <c r="T19" s="33">
-        <v>172260</v>
+        <v>7540</v>
       </c>
       <c r="U19" s="35">
         <f t="shared" si="1"/>
-        <v>243540</v>
+        <v>10660</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="45">
-        <v>11</v>
+        <v>19</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>69</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D20" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="46"/>
+      <c r="E20" s="186" t="s">
+        <v>125</v>
+      </c>
       <c r="F20" s="49">
-        <v>11.88</v>
+        <v>0.52</v>
       </c>
       <c r="G20" s="50">
-        <v>243540</v>
-      </c>
-      <c r="H20" s="51"/>
+        <v>9360.14</v>
+      </c>
+      <c r="H20" s="51">
+        <f>G20</f>
+        <v>9360.14</v>
+      </c>
       <c r="I20" s="52"/>
       <c r="J20" s="53">
         <f t="shared" si="2"/>
-        <v>243540</v>
+        <v>0</v>
       </c>
       <c r="K20" s="53">
         <f t="shared" si="3"/>
-        <v>7306.2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="54">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>57.199999999999996</v>
       </c>
       <c r="M20" s="54">
         <f t="shared" si="5"/>
-        <v>213840</v>
+        <v>7313.0798519999998</v>
       </c>
       <c r="N20" s="55">
         <v>0</v>
       </c>
       <c r="O20" s="56">
         <f t="shared" si="6"/>
-        <v>464686.11</v>
+        <v>7370.14</v>
       </c>
       <c r="P20" s="57">
         <f t="shared" si="0"/>
-        <v>478627.11</v>
+        <v>7591.14</v>
       </c>
       <c r="Q20" s="35">
         <f t="shared" si="7"/>
-        <v>0.10999999999999999</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="S20" s="33">
-        <v>3420</v>
+        <v>3120</v>
       </c>
       <c r="T20" s="33">
-        <v>8265</v>
+        <v>7540</v>
       </c>
       <c r="U20" s="35">
         <f t="shared" si="1"/>
-        <v>11685</v>
+        <v>10660</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D21" s="45" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E21" s="46"/>
       <c r="F21" s="49">
-        <v>0.56999999999999995</v>
+        <v>0.52</v>
       </c>
       <c r="G21" s="50">
-        <v>11685</v>
+        <v>20340.150000000001</v>
       </c>
       <c r="H21" s="51">
         <f>G21</f>
-        <v>11685</v>
+        <v>20340.150000000001</v>
       </c>
       <c r="I21" s="52"/>
       <c r="J21" s="53">
@@ -3954,61 +4127,61 @@
       </c>
       <c r="L21" s="54">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>57.199999999999996</v>
       </c>
       <c r="M21" s="54">
         <f t="shared" si="5"/>
-        <v>10259.999999999998</v>
+        <v>7313.0798519999998</v>
       </c>
       <c r="N21" s="55">
         <v>0</v>
       </c>
       <c r="O21" s="56">
         <f t="shared" si="6"/>
-        <v>10260.120000000001</v>
+        <v>7370.15</v>
       </c>
       <c r="P21" s="57">
         <f t="shared" si="0"/>
-        <v>10568.12</v>
+        <v>7591.15</v>
       </c>
       <c r="Q21" s="35">
         <f t="shared" si="7"/>
-        <v>0.11999999999999998</v>
+        <v>0.15</v>
       </c>
       <c r="S21" s="33">
-        <v>3120</v>
+        <v>3660</v>
       </c>
       <c r="T21" s="33">
-        <v>7540</v>
+        <v>8845</v>
       </c>
       <c r="U21" s="35">
         <f t="shared" si="1"/>
-        <v>10660</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1">
+        <v>12505</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1">
       <c r="A22" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D22" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="E22" s="46"/>
+        <v>91</v>
+      </c>
+      <c r="E22" s="45"/>
       <c r="F22" s="49">
-        <v>0.52</v>
+        <v>0.61</v>
       </c>
       <c r="G22" s="50">
-        <v>10660</v>
+        <v>10980.16</v>
       </c>
       <c r="H22" s="51">
         <f>G22</f>
-        <v>10660</v>
+        <v>10980.16</v>
       </c>
       <c r="I22" s="52"/>
       <c r="J22" s="53">
@@ -4021,429 +4194,230 @@
       </c>
       <c r="L22" s="54">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>67.099999999999994</v>
       </c>
       <c r="M22" s="54">
         <f t="shared" si="5"/>
-        <v>9360</v>
+        <v>8578.805210999999</v>
       </c>
       <c r="N22" s="55">
         <v>0</v>
       </c>
       <c r="O22" s="56">
         <f t="shared" si="6"/>
-        <v>9360.1299999999992</v>
+        <v>8646.16</v>
       </c>
       <c r="P22" s="57">
         <f t="shared" si="0"/>
-        <v>9641.1299999999992</v>
+        <v>8905.16</v>
       </c>
       <c r="Q22" s="35">
         <f t="shared" si="7"/>
-        <v>0.12999999999999998</v>
-      </c>
-      <c r="S22" s="33">
-        <v>3120</v>
-      </c>
-      <c r="T22" s="33">
-        <v>7540</v>
-      </c>
-      <c r="U22" s="35">
-        <f t="shared" si="1"/>
-        <v>10660</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1">
+        <v>0.16</v>
+      </c>
+      <c r="S22" s="34"/>
+    </row>
+    <row r="23" spans="1:21" ht="15.75" hidden="1" customHeight="1" thickBot="1">
       <c r="A23" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="46"/>
-      <c r="F23" s="49">
-        <v>0.52</v>
-      </c>
-      <c r="G23" s="50">
-        <v>10660</v>
-      </c>
-      <c r="H23" s="51">
-        <f>G23</f>
-        <v>10660</v>
-      </c>
-      <c r="I23" s="52"/>
-      <c r="J23" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="53">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23" s="51" t="str">
+        <f t="shared" ref="H23" si="8">G23</f>
+        <v>162450.31</v>
+      </c>
+      <c r="I23" s="59"/>
+      <c r="J23" s="60" t="e">
+        <f t="shared" ref="J23" si="9">G23-H23</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K23" s="53" t="e">
+        <f t="shared" ref="K23" si="10">IF(J23&gt;0,J23*3%,0)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="L23" s="54">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M23" s="54">
+      <c r="M23" s="61">
         <f t="shared" si="5"/>
-        <v>9360</v>
-      </c>
-      <c r="N23" s="55">
-        <v>0</v>
-      </c>
-      <c r="O23" s="56">
-        <f t="shared" si="6"/>
-        <v>9360.14</v>
-      </c>
-      <c r="P23" s="57">
-        <f t="shared" si="0"/>
-        <v>9641.14</v>
-      </c>
-      <c r="Q23" s="35">
-        <f t="shared" si="7"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="S23" s="33">
-        <v>3120</v>
-      </c>
-      <c r="T23" s="33">
-        <v>7540</v>
-      </c>
-      <c r="U23" s="35">
-        <f t="shared" si="1"/>
-        <v>10660</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="49">
-        <v>0.52</v>
-      </c>
-      <c r="G24" s="50">
-        <v>10660</v>
-      </c>
-      <c r="H24" s="51"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="53">
-        <f t="shared" si="2"/>
-        <v>10660</v>
-      </c>
-      <c r="K24" s="53">
-        <f t="shared" si="3"/>
-        <v>319.8</v>
-      </c>
-      <c r="L24" s="54">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="54">
-        <f t="shared" si="5"/>
-        <v>9360</v>
-      </c>
-      <c r="N24" s="55">
-        <v>0</v>
-      </c>
-      <c r="O24" s="56">
-        <f t="shared" si="6"/>
-        <v>20340.150000000001</v>
-      </c>
-      <c r="P24" s="57">
-        <f t="shared" si="0"/>
-        <v>20950.150000000001</v>
-      </c>
-      <c r="Q24" s="35">
-        <f t="shared" si="7"/>
-        <v>0.15</v>
-      </c>
-      <c r="S24" s="33">
-        <v>3660</v>
-      </c>
-      <c r="T24" s="33">
-        <v>8845</v>
-      </c>
-      <c r="U24" s="35">
-        <f t="shared" si="1"/>
-        <v>12505</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A25" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="45"/>
-      <c r="F25" s="49">
-        <v>0.61</v>
-      </c>
-      <c r="G25" s="50">
-        <v>12505</v>
-      </c>
-      <c r="H25" s="51">
-        <f>G25</f>
-        <v>12505</v>
-      </c>
-      <c r="I25" s="52"/>
-      <c r="J25" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="53">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="54">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="54">
-        <f t="shared" si="5"/>
-        <v>10980</v>
-      </c>
-      <c r="N25" s="55">
-        <v>0</v>
-      </c>
-      <c r="O25" s="56">
-        <f t="shared" si="6"/>
-        <v>10980.16</v>
-      </c>
-      <c r="P25" s="57">
-        <f t="shared" si="0"/>
-        <v>11309.16</v>
-      </c>
-      <c r="Q25" s="35">
-        <f t="shared" si="7"/>
-        <v>0.16</v>
-      </c>
-      <c r="S25" s="34"/>
-    </row>
-    <row r="26" spans="1:21" ht="15.75" hidden="1" customHeight="1" thickBot="1">
-      <c r="A26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="58" t="s">
-        <v>57</v>
-      </c>
-      <c r="H26" s="51" t="str">
-        <f t="shared" ref="H26" si="8">G26</f>
-        <v>162450.31</v>
-      </c>
-      <c r="I26" s="59"/>
-      <c r="J26" s="60" t="e">
-        <f t="shared" ref="J26" si="9">G26-H26</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K26" s="53" t="e">
-        <f t="shared" ref="K26" si="10">IF(J26&gt;0,J26*3%,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L26" s="54">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="61">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="62">
-        <v>0</v>
-      </c>
-      <c r="O26" s="56" t="e">
+        <v>0</v>
+      </c>
+      <c r="N23" s="62">
+        <v>0</v>
+      </c>
+      <c r="O23" s="56" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P26" s="57" t="e">
+      <c r="P23" s="57" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Q26" s="35"/>
-    </row>
-    <row r="27" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="B27" s="63"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="66">
-        <f>SUM(F10:F26)</f>
+      <c r="Q23" s="35"/>
+    </row>
+    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1">
+      <c r="B24" s="63"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="66">
+        <f>SUM(F7:F23)</f>
         <v>99.999999999999972</v>
       </c>
-      <c r="G27" s="40">
-        <f>SUM(G10:G26)</f>
-        <v>4547484.01</v>
-      </c>
-      <c r="H27" s="44">
-        <f>SUM(H10:H26)</f>
-        <v>1387751.09</v>
-      </c>
-      <c r="I27" s="44">
-        <f>SUM(I10:I26)</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="44"/>
-      <c r="K27" s="44"/>
-      <c r="L27" s="44">
-        <f>SUM(L10:L26)</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="44">
-        <f>SUM(M10:M26)</f>
-        <v>1800000</v>
-      </c>
-      <c r="N27" s="44">
-        <f>SUM(N10:N26)</f>
-        <v>0</v>
-      </c>
-      <c r="O27" s="67">
-        <f>SUM(O10:O25)</f>
-        <v>5054526.3599999994</v>
-      </c>
-      <c r="P27" s="67">
-        <f>SUM(P10:P25)</f>
-        <v>5206163.3599999994</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" ht="12.75" customHeight="1">
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-    </row>
-    <row r="29" spans="1:21" ht="15" hidden="1" customHeight="1"/>
-    <row r="30" spans="1:21" ht="9" customHeight="1">
-      <c r="D30" s="177" t="s">
+      <c r="G24" s="40">
+        <f>SUM(G7:G23)</f>
+        <v>5065159.3599999994</v>
+      </c>
+      <c r="H24" s="44">
+        <f>SUM(H7:H23)</f>
+        <v>2022091.92</v>
+      </c>
+      <c r="I24" s="44">
+        <f>SUM(I7:I23)</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44">
+        <f>SUM(L7:L23)</f>
+        <v>11000.000000000002</v>
+      </c>
+      <c r="M24" s="44">
+        <f>SUM(M7:M23)</f>
+        <v>1406361.5100000002</v>
+      </c>
+      <c r="N24" s="44">
+        <f>SUM(N7:N23)</f>
+        <v>480000</v>
+      </c>
+      <c r="O24" s="67">
+        <f>SUM(O7:O22)</f>
+        <v>5031739.3599999994</v>
+      </c>
+      <c r="P24" s="67">
+        <f>SUM(P7:P22)</f>
+        <v>5182689.3599999994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="12.75" customHeight="1">
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+    </row>
+    <row r="26" spans="1:21" ht="15" hidden="1" customHeight="1"/>
+    <row r="27" spans="1:21" ht="9" customHeight="1">
+      <c r="D27" s="169" t="s">
         <v>64</v>
       </c>
-      <c r="E30" s="177"/>
-      <c r="F30" s="177"/>
-      <c r="G30" s="177"/>
-      <c r="H30" s="177"/>
-      <c r="I30" s="177"/>
-      <c r="J30" s="177"/>
-      <c r="K30" s="177"/>
-      <c r="L30" s="177"/>
-      <c r="M30" s="177"/>
-      <c r="N30" s="177"/>
-      <c r="O30" s="177"/>
+      <c r="E27" s="169"/>
+      <c r="F27" s="169"/>
+      <c r="G27" s="169"/>
+      <c r="H27" s="169"/>
+      <c r="I27" s="169"/>
+      <c r="J27" s="169"/>
+      <c r="K27" s="169"/>
+      <c r="L27" s="169"/>
+      <c r="M27" s="169"/>
+      <c r="N27" s="169"/>
+      <c r="O27" s="169"/>
+    </row>
+    <row r="28" spans="1:21" ht="12" hidden="1" customHeight="1">
+      <c r="D28" s="169"/>
+      <c r="E28" s="169"/>
+      <c r="F28" s="169"/>
+      <c r="G28" s="169"/>
+      <c r="H28" s="169"/>
+      <c r="I28" s="169"/>
+      <c r="J28" s="169"/>
+      <c r="K28" s="169"/>
+      <c r="L28" s="169"/>
+      <c r="M28" s="169"/>
+      <c r="N28" s="169"/>
+      <c r="O28" s="169"/>
+    </row>
+    <row r="29" spans="1:21" ht="12" hidden="1" customHeight="1">
+      <c r="D29" s="169"/>
+      <c r="E29" s="169"/>
+      <c r="F29" s="169"/>
+      <c r="G29" s="169"/>
+      <c r="H29" s="169"/>
+      <c r="I29" s="169"/>
+      <c r="J29" s="169"/>
+      <c r="K29" s="169"/>
+      <c r="L29" s="169"/>
+      <c r="M29" s="169"/>
+      <c r="N29" s="169"/>
+      <c r="O29" s="169"/>
+    </row>
+    <row r="30" spans="1:21" ht="12" hidden="1" customHeight="1">
+      <c r="D30" s="169"/>
+      <c r="E30" s="169"/>
+      <c r="F30" s="169"/>
+      <c r="G30" s="169"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="169"/>
+      <c r="J30" s="169"/>
+      <c r="K30" s="169"/>
+      <c r="L30" s="169"/>
+      <c r="M30" s="169"/>
+      <c r="N30" s="169"/>
+      <c r="O30" s="169"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="177"/>
-      <c r="E31" s="177"/>
-      <c r="F31" s="177"/>
-      <c r="G31" s="177"/>
-      <c r="H31" s="177"/>
-      <c r="I31" s="177"/>
-      <c r="J31" s="177"/>
-      <c r="K31" s="177"/>
-      <c r="L31" s="177"/>
-      <c r="M31" s="177"/>
-      <c r="N31" s="177"/>
-      <c r="O31" s="177"/>
-    </row>
-    <row r="32" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D32" s="177"/>
-      <c r="E32" s="177"/>
-      <c r="F32" s="177"/>
-      <c r="G32" s="177"/>
-      <c r="H32" s="177"/>
-      <c r="I32" s="177"/>
-      <c r="J32" s="177"/>
-      <c r="K32" s="177"/>
-      <c r="L32" s="177"/>
-      <c r="M32" s="177"/>
-      <c r="N32" s="177"/>
-      <c r="O32" s="177"/>
-    </row>
-    <row r="33" spans="4:15" ht="12" hidden="1" customHeight="1">
-      <c r="D33" s="177"/>
-      <c r="E33" s="177"/>
-      <c r="F33" s="177"/>
-      <c r="G33" s="177"/>
-      <c r="H33" s="177"/>
-      <c r="I33" s="177"/>
-      <c r="J33" s="177"/>
-      <c r="K33" s="177"/>
-      <c r="L33" s="177"/>
-      <c r="M33" s="177"/>
-      <c r="N33" s="177"/>
-      <c r="O33" s="177"/>
-    </row>
-    <row r="34" spans="4:15" ht="12" hidden="1" customHeight="1">
-      <c r="D34" s="177"/>
-      <c r="E34" s="177"/>
-      <c r="F34" s="177"/>
-      <c r="G34" s="177"/>
-      <c r="H34" s="177"/>
-      <c r="I34" s="177"/>
-      <c r="J34" s="177"/>
-      <c r="K34" s="177"/>
-      <c r="L34" s="177"/>
-      <c r="M34" s="177"/>
-      <c r="N34" s="177"/>
-      <c r="O34" s="177"/>
-    </row>
-    <row r="35" spans="4:15" ht="65.25" customHeight="1">
-      <c r="D35" s="177"/>
-      <c r="E35" s="177"/>
-      <c r="F35" s="177"/>
-      <c r="G35" s="177"/>
-      <c r="H35" s="177"/>
-      <c r="I35" s="177"/>
-      <c r="J35" s="177"/>
-      <c r="K35" s="177"/>
-      <c r="L35" s="177"/>
-      <c r="M35" s="177"/>
-      <c r="N35" s="177"/>
-      <c r="O35" s="177"/>
+      <c r="D31" s="169"/>
+      <c r="E31" s="169"/>
+      <c r="F31" s="169"/>
+      <c r="G31" s="169"/>
+      <c r="H31" s="169"/>
+      <c r="I31" s="169"/>
+      <c r="J31" s="169"/>
+      <c r="K31" s="169"/>
+      <c r="L31" s="169"/>
+      <c r="M31" s="169"/>
+      <c r="N31" s="169"/>
+      <c r="O31" s="169"/>
+    </row>
+    <row r="32" spans="1:21" ht="65.25" customHeight="1">
+      <c r="D32" s="169"/>
+      <c r="E32" s="169"/>
+      <c r="F32" s="169"/>
+      <c r="G32" s="169"/>
+      <c r="H32" s="169"/>
+      <c r="I32" s="169"/>
+      <c r="J32" s="169"/>
+      <c r="K32" s="169"/>
+      <c r="L32" s="169"/>
+      <c r="M32" s="169"/>
+      <c r="N32" s="169"/>
+      <c r="O32" s="169"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="18">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="D30:O35"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="D27:O32"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
-    <mergeCell ref="B5:P7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
